--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105365_W4.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105365_W4.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5235</v>
+        <v>5.6667</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1993</v>
+        <v>7.5605</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6758</v>
+        <v>-1.8937</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0893</v>
+        <v>5.1778</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5041</v>
+        <v>5.5215</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4148</v>
+        <v>-0.3437</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8751</v>
+        <v>7.2805</v>
       </c>
       <c r="K2" t="n">
-        <v>6.3153</v>
+        <v>6.5062</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5598</v>
+        <v>0.7743</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7858</v>
+        <v>-2.1028</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8112</v>
+        <v>-0.9847</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9745</v>
+        <v>-1.118</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.399</v>
+        <v>-1.377</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3695</v>
+        <v>0.3938</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0549</v>
+        <v>0.9519</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6855</v>
+        <v>-0.5581</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4637</v>
+        <v>1.4722</v>
       </c>
       <c r="W2" t="n">
-        <v>1.601</v>
+        <v>1.623</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6545</v>
+        <v>3.5813</v>
       </c>
       <c r="E3" t="n">
-        <v>5.943</v>
+        <v>6.0594</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2885</v>
+        <v>-2.4781</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4552</v>
+        <v>2.3359</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3651</v>
+        <v>1.3018</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0901</v>
+        <v>1.0342</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2139</v>
+        <v>4.3739</v>
       </c>
       <c r="K3" t="n">
-        <v>2.011</v>
+        <v>2.1072</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2029</v>
+        <v>2.2667</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7587</v>
+        <v>-2.038</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6459</v>
+        <v>-0.8054</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1128</v>
+        <v>-1.2326</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2332</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5024</v>
+        <v>0.5437</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7603</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2579</v>
+        <v>-0.1252</v>
       </c>
       <c r="V3" t="n">
-        <v>0.93</v>
+        <v>0.9312</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1347</v>
+        <v>2.164</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2046</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4718</v>
+        <v>3.5148</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1276</v>
+        <v>5.359</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6558</v>
+        <v>-1.8441</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2673</v>
+        <v>3.2684</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5824</v>
+        <v>3.5783</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3151</v>
+        <v>-0.3099</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3597</v>
+        <v>5.6474</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7304</v>
+        <v>4.8864</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6293</v>
+        <v>0.761</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0924</v>
+        <v>-2.379</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1479</v>
+        <v>-1.3081</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9444</v>
+        <v>-1.0709</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9327</v>
+        <v>-0.918</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R4" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1371</v>
+        <v>1.1644</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0322</v>
+        <v>0.9245</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1049</v>
+        <v>0.2399</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8443</v>
+        <v>1.6789</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9528</v>
+        <v>2.9473</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1085</v>
+        <v>-1.2684</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4302</v>
+        <v>1.2898</v>
       </c>
       <c r="H5" t="n">
-        <v>2.718</v>
+        <v>2.674</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2877</v>
+        <v>-1.3842</v>
       </c>
       <c r="J5" t="n">
-        <v>2.866</v>
+        <v>2.9251</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5358</v>
+        <v>2.5917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3301</v>
+        <v>0.3335</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4357</v>
+        <v>-1.6353</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1821</v>
+        <v>0.0824</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6179</v>
+        <v>-1.7176</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S5" t="n">
-        <v>1.085</v>
+        <v>1.081</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2527</v>
+        <v>1.1696</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1677</v>
+        <v>-0.0887</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.6919</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1438</v>
+        <v>0.0815</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6204</v>
+        <v>2.7115</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4766</v>
+        <v>-2.63</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8222</v>
+        <v>-0.7977</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4278</v>
+        <v>0.3646</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.25</v>
+        <v>-1.1622</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1227</v>
+        <v>2.3281</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4181</v>
+        <v>1.4493</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7046</v>
+        <v>0.8788</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9449</v>
+        <v>-3.1258</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9903</v>
+        <v>-1.0847</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9546</v>
+        <v>-2.041</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8675</v>
+        <v>0.8137</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4977</v>
+        <v>0.3834</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3698</v>
+        <v>0.4303</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0547</v>
+        <v>-0.1205</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6839</v>
+        <v>0.7357</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7386</v>
+        <v>-0.8562</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7526</v>
+        <v>-1.7813</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2715</v>
+        <v>0.2464</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0241</v>
+        <v>-2.0277</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2561</v>
+        <v>0.3892</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.408</v>
+        <v>-0.3651</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6641</v>
+        <v>0.7543</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0087</v>
+        <v>-2.1705</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6796</v>
+        <v>0.6115</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6883</v>
+        <v>-2.782</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3948</v>
+        <v>0.3625</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2906</v>
+        <v>0.1956</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1042</v>
+        <v>0.1669</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1373</v>
+        <v>0.1509</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1373</v>
+        <v>0.1509</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,19 +1068,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1668</v>
+        <v>-0.1705</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1668</v>
+        <v>-0.1705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1699</v>
+        <v>0.1529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1699</v>
+        <v>0.1529</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1699</v>
+        <v>0.1529</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1699</v>
+        <v>0.1529</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3367</v>
+        <v>-0.3234</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3367</v>
+        <v>-0.3234</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4654</v>
+        <v>-0.4269</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8955</v>
+        <v>2.157</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3609</v>
+        <v>-2.5839</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2227</v>
+        <v>-0.2092</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3168</v>
+        <v>-0.438</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0941</v>
+        <v>0.2288</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2396</v>
+        <v>2.5227</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.8525</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4054</v>
+        <v>1.6702</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4623</v>
+        <v>-2.7319</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.151</v>
+        <v>-1.2905</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3113</v>
+        <v>-1.4414</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9232</v>
+        <v>0.9297</v>
       </c>
       <c r="T9" t="n">
-        <v>0.783</v>
+        <v>0.6963</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1402</v>
+        <v>0.2334</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2046</v>
+        <v>1.2329</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2046</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7254</v>
+        <v>-1.7188</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4695</v>
+        <v>-0.366</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2559</v>
+        <v>-1.3528</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2757</v>
+        <v>-2.2404</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8752</v>
+        <v>-0.8426</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4005</v>
+        <v>-1.3978</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3543</v>
+        <v>-0.2289</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3833</v>
+        <v>-1.31</v>
       </c>
       <c r="L10" t="n">
-        <v>1.029</v>
+        <v>1.0811</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9214</v>
+        <v>-2.0115</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5081</v>
+        <v>0.4674</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4296</v>
+        <v>-2.479</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5503</v>
+        <v>0.5216</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0167</v>
+        <v>-0.0717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5671</v>
+        <v>0.5933</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4174</v>
+        <v>-3.3853</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0643</v>
+        <v>-1.9308</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3531</v>
+        <v>-1.4545</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8335</v>
+        <v>-4.7658</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2623</v>
+        <v>-0.2993</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.5712</v>
+        <v>-4.4665</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.482</v>
+        <v>-3.3071</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7751</v>
+        <v>-0.7402</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7069</v>
+        <v>-2.5669</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3515</v>
+        <v>-1.4587</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5127</v>
+        <v>0.441</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8643</v>
+        <v>-1.8996</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1131</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2131</v>
+        <v>0.1434</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1</v>
+        <v>-0.0613</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1373</v>
+        <v>0.1509</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2046</v>
+        <v>1.2329</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,64 +1400,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7613</v>
+        <v>-5.6462</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1044</v>
+        <v>-5.8704</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3432</v>
+        <v>0.2242</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.5129</v>
+        <v>-5.3864</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.3551</v>
+        <v>-3.1903</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1577</v>
+        <v>-2.1961</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.7343</v>
+        <v>-3.4629</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.6995</v>
+        <v>-3.4696</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0348</v>
+        <v>0.0067</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7786</v>
+        <v>-1.9234</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3444</v>
+        <v>0.2793</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.123</v>
+        <v>-2.2027</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0985</v>
+        <v>-2.0655</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4975</v>
+        <v>-3.4424</v>
       </c>
       <c r="R12" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7128</v>
+        <v>1.6547</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9901</v>
+        <v>0.8841</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7227</v>
+        <v>0.7706</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1373</v>
+        <v>0.1509</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1373</v>
+        <v>0.1509</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.046899999999999</v>
+        <v>3.055</v>
       </c>
       <c r="E13" t="n">
-        <v>17.7843</v>
+        <v>19.3632</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.7373</v>
+        <v>-16.308</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.007700000000001</v>
+        <v>-2.956000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>9.2294</v>
+        <v>9.0693</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.2369</v>
+        <v>-12.0251</v>
       </c>
       <c r="J13" t="n">
-        <v>16.3625</v>
+        <v>18.468</v>
       </c>
       <c r="K13" t="n">
-        <v>11.5789</v>
+        <v>12.5084</v>
       </c>
       <c r="L13" t="n">
-        <v>4.7835</v>
+        <v>5.9597</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.3701</v>
+        <v>-21.424</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3495</v>
+        <v>-3.4389</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.0207</v>
+        <v>-17.9848</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3318</v>
+        <v>-2.295</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.99</v>
+        <v>-13.7699</v>
       </c>
       <c r="R13" t="n">
-        <v>11.6582</v>
+        <v>11.475</v>
       </c>
       <c r="S13" t="n">
-        <v>7.319000000000001</v>
+        <v>7.2238</v>
       </c>
       <c r="T13" t="n">
-        <v>6.857899999999999</v>
+        <v>5.946</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4611000000000002</v>
+        <v>1.2777</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0674</v>
+        <v>1.0822</v>
       </c>
       <c r="W13" t="n">
-        <v>8.554099999999998</v>
+        <v>8.7186</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.486599999999999</v>
+        <v>-7.6366</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8568</v>
+        <v>4.0921</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6161</v>
+        <v>6.0255</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7593</v>
+        <v>-1.9334</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7139</v>
+        <v>2.9309</v>
       </c>
       <c r="H14" t="n">
-        <v>1.603</v>
+        <v>1.742</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1109</v>
+        <v>1.1889</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9475</v>
+        <v>5.4069</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7641</v>
+        <v>4.0027</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1834</v>
+        <v>1.4042</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2337</v>
+        <v>-2.4759</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1612</v>
+        <v>-2.2606</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0725</v>
+        <v>-0.2153</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2332</v>
+        <v>0.2295</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R14" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2948</v>
+        <v>-0.3012</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.0078</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.391</v>
+        <v>-0.2934</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2046</v>
+        <v>1.2329</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7383</v>
+        <v>1.7739</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5337</v>
+        <v>-0.541</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8638</v>
+        <v>2.847</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9555</v>
+        <v>3.071</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.2239</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8173</v>
+        <v>3.7739</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5611</v>
+        <v>-0.615</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3784</v>
+        <v>4.3889</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4807</v>
+        <v>3.6421</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7417</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2224</v>
+        <v>4.3482</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3367</v>
+        <v>0.1318</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1806</v>
+        <v>0.0912</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1561</v>
+        <v>0.0406</v>
       </c>
       <c r="P15" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2853</v>
+        <v>-1.2218</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5251</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7601</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3738</v>
+        <v>2.3331</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2991</v>
+        <v>1.3273</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0748</v>
+        <v>1.0059</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2402</v>
+        <v>1.2013</v>
       </c>
       <c r="H16" t="n">
-        <v>0.405</v>
+        <v>0.3828</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8185</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5229</v>
+        <v>1.5867</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5672</v>
+        <v>0.5797</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9557</v>
+        <v>1.007</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2827</v>
+        <v>-0.3854</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1622</v>
+        <v>-0.1969</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1204</v>
+        <v>-0.1885</v>
       </c>
       <c r="P16" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2654</v>
+        <v>-0.2451</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2238</v>
+        <v>-0.2595</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0416</v>
+        <v>0.0143</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9361</v>
+        <v>1.7659</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0265</v>
+        <v>4.0261</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0905</v>
+        <v>-2.2602</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2451</v>
+        <v>1.1384</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1906</v>
+        <v>1.1753</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0545</v>
+        <v>-0.0369</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5482</v>
+        <v>3.6557</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5192</v>
+        <v>2.5746</v>
       </c>
       <c r="L17" t="n">
-        <v>1.029</v>
+        <v>1.0811</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3031</v>
+        <v>-2.5173</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3285</v>
+        <v>-1.3993</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9745</v>
+        <v>-1.118</v>
       </c>
       <c r="P17" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3593</v>
+        <v>0.3325</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4783</v>
+        <v>0.3703</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1191</v>
+        <v>-0.0378</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5693</v>
+        <v>0.5208</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6088</v>
+        <v>0.6018</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0395</v>
+        <v>-0.081</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4831</v>
+        <v>0.4487</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1471</v>
+        <v>-0.1711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6302</v>
+        <v>0.6198</v>
       </c>
       <c r="J18" t="n">
-        <v>0.677</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0167</v>
+        <v>0.0171</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6603</v>
+        <v>0.6669</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1939</v>
+        <v>-0.2353</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1638</v>
+        <v>-0.1881</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0301</v>
+        <v>-0.0471</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2332</v>
+        <v>0.2295</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2332</v>
+        <v>0.2295</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0097</v>
+        <v>-0.0065</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0585</v>
+        <v>0.0756</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6175</v>
+        <v>-0.615</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0771</v>
+        <v>0.2232</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6946</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5541</v>
+        <v>-1.5566</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.489</v>
+        <v>-2.4089</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9349</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0821</v>
+        <v>-0.9094</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9992</v>
+        <v>-1.8357</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9171</v>
+        <v>0.9263</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.472</v>
+        <v>-0.6472</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4898</v>
+        <v>-0.5732</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0178</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0065</v>
+        <v>0.0104</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1904</v>
+        <v>0.1161</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1839</v>
+        <v>-0.1056</v>
       </c>
       <c r="V19" t="n">
-        <v>0.93</v>
+        <v>0.9312</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1347</v>
+        <v>2.164</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2046</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7097</v>
+        <v>-1.6882</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4997</v>
+        <v>1.7466</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2095</v>
+        <v>-3.4347</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3673</v>
+        <v>-1.382</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0936</v>
+        <v>-1.0554</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2737</v>
+        <v>-0.3266</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4959</v>
+        <v>2.7729</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0615</v>
+        <v>1.2405</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4345</v>
+        <v>1.5324</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8632</v>
+        <v>-4.1549</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.155</v>
+        <v>-2.2959</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7082</v>
+        <v>-1.859</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6995</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6322</v>
+        <v>1.6065</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9848</v>
+        <v>-1.0014</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1437</v>
+        <v>-0.266</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8411</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3419</v>
+        <v>1.3838</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4792</v>
+        <v>1.5346</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1373</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.186</v>
+        <v>-2.2405</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9704</v>
+        <v>1.0238</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1563</v>
+        <v>-3.2643</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7759</v>
+        <v>-1.7883</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7553</v>
+        <v>-0.7408</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0206</v>
+        <v>-1.0475</v>
       </c>
       <c r="J21" t="n">
-        <v>0.945</v>
+        <v>1.0551</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5763</v>
+        <v>0.6408</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3687</v>
+        <v>0.4142</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7209</v>
+        <v>-2.8434</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3316</v>
+        <v>-1.3817</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3893</v>
+        <v>-1.4617</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1658</v>
+        <v>1.1475</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5177</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0254</v>
+        <v>-0.0313</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.534</v>
+        <v>-0.4864</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3207</v>
+        <v>-2.3361</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6998</v>
+        <v>-2.6314</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3791</v>
+        <v>0.2953</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3907</v>
+        <v>-0.4506</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1573</v>
+        <v>-1.1412</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7665</v>
+        <v>0.6906</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6494</v>
+        <v>-0.5621</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8328</v>
+        <v>-0.7473</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1834</v>
+        <v>0.1853</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2586</v>
+        <v>0.1115</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3245</v>
+        <v>-0.3939</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5831</v>
+        <v>0.5054</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6322</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3317</v>
+        <v>-2.295</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6995</v>
+        <v>0.6885</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2978</v>
+        <v>-0.279</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2813</v>
+        <v>0.2256</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5046</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5162</v>
+        <v>-2.4622</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9954</v>
+        <v>-0.7275</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5208</v>
+        <v>-1.7347</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8128</v>
+        <v>0.8003</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.55</v>
+        <v>-1.5945</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3628</v>
+        <v>2.3948</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8664</v>
+        <v>2.1532</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2322</v>
+        <v>-0.1335</v>
       </c>
       <c r="L23" t="n">
-        <v>2.0986</v>
+        <v>2.2867</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0536</v>
+        <v>-1.3529</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3178</v>
+        <v>-1.461</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2642</v>
+        <v>0.1081</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0985</v>
+        <v>-2.0655</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4975</v>
+        <v>-3.4424</v>
       </c>
       <c r="R23" t="n">
-        <v>1.399</v>
+        <v>1.377</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2305</v>
+        <v>-1.197</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4316</v>
+        <v>-0.5203</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.6768</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0673</v>
+        <v>-1.082</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8068</v>
+        <v>-3.7855</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3791</v>
+        <v>1.6217</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.1859</v>
+        <v>-5.4072</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2167</v>
+        <v>-2.1601</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.6745</v>
+        <v>-4.6425</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4578</v>
+        <v>2.4824</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6179</v>
+        <v>1.9389</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3496</v>
+        <v>-2.1937</v>
       </c>
       <c r="L24" t="n">
-        <v>3.9675</v>
+        <v>4.1326</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.8347</v>
+        <v>-4.099</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.3249</v>
+        <v>-2.4488</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5097</v>
+        <v>-1.6502</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9327</v>
+        <v>0.918</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1658</v>
+        <v>-1.1475</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0985</v>
+        <v>2.0655</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3182</v>
+        <v>-1.3105</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1403</v>
+        <v>-0.2517</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1778</v>
+        <v>-1.0588</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2046</v>
+        <v>-1.2329</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0673</v>
+        <v>1.082</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2719</v>
+        <v>-2.3149</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5571</v>
+        <v>-1.5686</v>
       </c>
       <c r="E25" t="n">
-        <v>14.7371</v>
+        <v>16.3081</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.2943</v>
+        <v>-17.8764</v>
       </c>
       <c r="G25" t="n">
-        <v>3.007700000000001</v>
+        <v>2.9559</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.229299999999999</v>
+        <v>-9.0693</v>
       </c>
       <c r="I25" t="n">
-        <v>12.2369</v>
+        <v>12.0252</v>
       </c>
       <c r="J25" t="n">
-        <v>19.37</v>
+        <v>21.424</v>
       </c>
       <c r="K25" t="n">
-        <v>2.349500000000001</v>
+        <v>3.439099999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>17.0206</v>
+        <v>17.9849</v>
       </c>
       <c r="M25" t="n">
-        <v>-16.3625</v>
+        <v>-18.468</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.5787</v>
+        <v>-12.5082</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.7835</v>
+        <v>-5.9596</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3317</v>
+        <v>2.295</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.6583</v>
+        <v>-11.4749</v>
       </c>
       <c r="R25" t="n">
-        <v>13.99</v>
+        <v>13.77</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.8293</v>
+        <v>-5.7373</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.461</v>
+        <v>-1.2778</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.3681</v>
+        <v>-4.4596</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.067299999999999</v>
+        <v>-1.0819</v>
       </c>
       <c r="W25" t="n">
-        <v>7.486799999999999</v>
+        <v>7.6365</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.554</v>
+        <v>-8.7186</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105365_W4.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105365_W4.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6667</v>
+        <v>5.546</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5605</v>
+        <v>7.1906</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8937</v>
+        <v>-1.6447</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1778</v>
+        <v>5.0617</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5215</v>
+        <v>5.4174</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3437</v>
+        <v>-0.3558</v>
       </c>
       <c r="J2" t="n">
-        <v>7.2805</v>
+        <v>7.0348</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5062</v>
+        <v>6.3149</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7743</v>
+        <v>0.7199</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1028</v>
+        <v>-1.9731</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9847</v>
+        <v>-0.8975</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.118</v>
+        <v>-1.0757</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R2" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3938</v>
+        <v>0.4263</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9519</v>
+        <v>0.8994</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5581</v>
+        <v>-0.4731</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4722</v>
+        <v>1.4619</v>
       </c>
       <c r="W2" t="n">
-        <v>1.623</v>
+        <v>1.5962</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5813</v>
+        <v>3.6312</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0594</v>
+        <v>5.8368</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4781</v>
+        <v>-2.2056</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3359</v>
+        <v>2.3405</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3018</v>
+        <v>1.3044</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0342</v>
+        <v>1.0361</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3739</v>
+        <v>4.2617</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1072</v>
+        <v>2.0314</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2667</v>
+        <v>2.2303</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.038</v>
+        <v>-1.9212</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8054</v>
+        <v>-0.727</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2326</v>
+        <v>-1.1942</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R3" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5437</v>
+        <v>0.5948</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6167</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1252</v>
+        <v>-0.0219</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9312</v>
+        <v>0.9298</v>
       </c>
       <c r="W3" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5148</v>
+        <v>3.4976</v>
       </c>
       <c r="E4" t="n">
-        <v>5.359</v>
+        <v>5.0541</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8441</v>
+        <v>-1.5566</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2684</v>
+        <v>3.2091</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5783</v>
+        <v>3.5171</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3099</v>
+        <v>-0.308</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6474</v>
+        <v>5.4624</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8864</v>
+        <v>4.7376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.761</v>
+        <v>0.7248</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.379</v>
+        <v>-2.2533</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3081</v>
+        <v>-1.2206</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0709</v>
+        <v>-1.0327</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R4" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1644</v>
+        <v>1.2243</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9245</v>
+        <v>0.8673</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2399</v>
+        <v>0.357</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6789</v>
+        <v>1.7418</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9473</v>
+        <v>2.8236</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2684</v>
+        <v>-1.0818</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2898</v>
+        <v>1.2953</v>
       </c>
       <c r="H5" t="n">
-        <v>2.674</v>
+        <v>2.6448</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3842</v>
+        <v>-1.3494</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9251</v>
+        <v>2.8531</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5917</v>
+        <v>2.5236</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3335</v>
+        <v>0.3294</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6353</v>
+        <v>-1.5577</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0824</v>
+        <v>0.1211</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7176</v>
+        <v>-1.6789</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S5" t="n">
-        <v>1.081</v>
+        <v>1.1128</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1696</v>
+        <v>1.1404</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0887</v>
+        <v>-0.0276</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0815</v>
+        <v>0.1161</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7115</v>
+        <v>2.5466</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.63</v>
+        <v>-2.4306</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7977</v>
+        <v>-0.7862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3646</v>
+        <v>0.3836</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1622</v>
+        <v>-1.1698</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3281</v>
+        <v>2.2434</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4493</v>
+        <v>1.4112</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8788</v>
+        <v>0.8321</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1258</v>
+        <v>-3.0295</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0847</v>
+        <v>-1.0276</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.041</v>
+        <v>-2.0019</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8137</v>
+        <v>0.7965</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3834</v>
+        <v>0.3033</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4303</v>
+        <v>0.4932</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1205</v>
+        <v>-0.1024</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7357</v>
+        <v>0.6105</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8562</v>
+        <v>-0.7129</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7813</v>
+        <v>-1.7546</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2464</v>
+        <v>0.2522</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0277</v>
+        <v>-2.0068</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3892</v>
+        <v>0.3512</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3651</v>
+        <v>-0.376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7543</v>
+        <v>0.7272</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1705</v>
+        <v>-2.1058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6115</v>
+        <v>0.6282</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.782</v>
+        <v>-2.734</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3625</v>
+        <v>0.3481</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1956</v>
+        <v>0.125</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1669</v>
+        <v>0.223</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,19 +1068,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1529</v>
+        <v>0.157</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1529</v>
+        <v>0.157</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1529</v>
+        <v>0.157</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1529</v>
+        <v>0.157</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3234</v>
+        <v>-0.3231</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3234</v>
+        <v>-0.3231</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4269</v>
+        <v>-0.3889</v>
       </c>
       <c r="E9" t="n">
-        <v>2.157</v>
+        <v>1.9335</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5839</v>
+        <v>-2.3224</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2092</v>
+        <v>-0.1842</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.438</v>
+        <v>-0.3814</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2288</v>
+        <v>0.1972</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5227</v>
+        <v>2.4261</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8525</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6702</v>
+        <v>1.5959</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7319</v>
+        <v>-2.6103</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2905</v>
+        <v>-1.2116</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4414</v>
+        <v>-1.3987</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9297</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6963</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2334</v>
+        <v>0.3165</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7188</v>
+        <v>-1.7102</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.366</v>
+        <v>-0.4818</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3528</v>
+        <v>-1.2284</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2404</v>
+        <v>-2.2255</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8426</v>
+        <v>-0.8409</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3978</v>
+        <v>-1.3846</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2289</v>
+        <v>-0.2575</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.31</v>
+        <v>-1.3165</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0811</v>
+        <v>1.059</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0115</v>
+        <v>-1.968</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4674</v>
+        <v>0.4756</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.479</v>
+        <v>-2.4436</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5216</v>
+        <v>0.5152</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0717</v>
+        <v>-0.1186</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5933</v>
+        <v>0.6338</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3853</v>
+        <v>-3.3602</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9308</v>
+        <v>-2.0231</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4545</v>
+        <v>-1.3371</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7658</v>
+        <v>-4.7241</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2993</v>
+        <v>-0.2791</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.4665</v>
+        <v>-4.445</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3071</v>
+        <v>-3.3132</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7402</v>
+        <v>-0.7413</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5669</v>
+        <v>-2.5719</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4587</v>
+        <v>-1.4109</v>
       </c>
       <c r="N11" t="n">
-        <v>0.441</v>
+        <v>0.4622</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8996</v>
+        <v>-1.8731</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0598</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1434</v>
+        <v>0.0917</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0613</v>
+        <v>-0.0319</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,64 +1400,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6462</v>
+        <v>-5.6767</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8704</v>
+        <v>-6.0521</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2242</v>
+        <v>0.3754</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3864</v>
+        <v>-5.3666</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1903</v>
+        <v>-3.2007</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1961</v>
+        <v>-2.1659</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.4629</v>
+        <v>-3.5038</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.4696</v>
+        <v>-3.5013</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0067</v>
+        <v>-0.0024</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9234</v>
+        <v>-1.8628</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2793</v>
+        <v>0.3006</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2027</v>
+        <v>-2.1635</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0655</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R12" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6547</v>
+        <v>1.6614</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8841</v>
+        <v>0.827</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7706</v>
+        <v>0.8344</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.055</v>
+        <v>3.128299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>19.3632</v>
+        <v>17.4387</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.308</v>
+        <v>-14.3107</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.956000000000001</v>
+        <v>-2.977599999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>9.0693</v>
+        <v>8.974400000000003</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.0251</v>
+        <v>-11.952</v>
       </c>
       <c r="J13" t="n">
-        <v>18.468</v>
+        <v>17.5582</v>
       </c>
       <c r="K13" t="n">
-        <v>12.5084</v>
+        <v>11.9137</v>
       </c>
       <c r="L13" t="n">
-        <v>5.9597</v>
+        <v>5.644300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.424</v>
+        <v>-20.5356</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.4389</v>
+        <v>-2.9396</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.9848</v>
+        <v>-17.5963</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.295</v>
+        <v>-2.3396</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.7699</v>
+        <v>-14.0384</v>
       </c>
       <c r="R13" t="n">
-        <v>11.475</v>
+        <v>11.6988</v>
       </c>
       <c r="S13" t="n">
-        <v>7.2238</v>
+        <v>7.3813</v>
       </c>
       <c r="T13" t="n">
-        <v>5.946</v>
+        <v>5.4009</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2777</v>
+        <v>1.9803</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0822</v>
+        <v>1.0641</v>
       </c>
       <c r="W13" t="n">
-        <v>8.7186</v>
+        <v>8.517999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.6366</v>
+        <v>-7.4539</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0921</v>
+        <v>3.9316</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0255</v>
+        <v>5.6467</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9334</v>
+        <v>-1.715</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9309</v>
+        <v>2.8154</v>
       </c>
       <c r="H14" t="n">
-        <v>1.742</v>
+        <v>1.6554</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1889</v>
+        <v>1.1601</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4069</v>
+        <v>5.1783</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0027</v>
+        <v>3.8362</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4042</v>
+        <v>1.3421</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4759</v>
+        <v>-2.3629</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2606</v>
+        <v>-2.1808</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2153</v>
+        <v>-0.1821</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R14" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3012</v>
+        <v>-0.3162</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0078</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2934</v>
+        <v>-0.2239</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7739</v>
+        <v>1.7305</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.847</v>
+        <v>2.8902</v>
       </c>
       <c r="E15" t="n">
-        <v>3.071</v>
+        <v>2.9427</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2239</v>
+        <v>-0.0525</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7739</v>
+        <v>3.7606</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.615</v>
+        <v>-0.5825</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3889</v>
+        <v>4.343</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6421</v>
+        <v>3.5696</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7081</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3482</v>
+        <v>4.2777</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1318</v>
+        <v>0.191</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0912</v>
+        <v>0.1256</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0406</v>
+        <v>0.0654</v>
       </c>
       <c r="P15" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2218</v>
+        <v>-1.2101</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3331</v>
+        <v>2.3662</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3273</v>
+        <v>1.2536</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0059</v>
+        <v>1.1126</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2013</v>
+        <v>1.199</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3828</v>
+        <v>0.385</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8185</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5867</v>
+        <v>1.5503</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5797</v>
+        <v>0.5645</v>
       </c>
       <c r="L16" t="n">
-        <v>1.007</v>
+        <v>0.9858</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3854</v>
+        <v>-0.3513</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1969</v>
+        <v>-0.1795</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1885</v>
+        <v>-0.1718</v>
       </c>
       <c r="P16" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2451</v>
+        <v>-0.2367</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2595</v>
+        <v>-0.2968</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0143</v>
+        <v>0.0601</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7659</v>
+        <v>1.8056</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0261</v>
+        <v>3.861</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2602</v>
+        <v>-2.0554</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1384</v>
+        <v>1.1442</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1753</v>
+        <v>1.1608</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0369</v>
+        <v>-0.0166</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6557</v>
+        <v>3.5661</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5746</v>
+        <v>2.507</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0811</v>
+        <v>1.059</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5173</v>
+        <v>-2.4218</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3993</v>
+        <v>-1.3462</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.118</v>
+        <v>-1.0757</v>
       </c>
       <c r="P17" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3325</v>
+        <v>0.3216</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3703</v>
+        <v>0.2949</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0378</v>
+        <v>0.0267</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5208</v>
+        <v>0.553</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6018</v>
+        <v>0.5793</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.081</v>
+        <v>-0.0263</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4487</v>
+        <v>0.4575</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1711</v>
+        <v>-0.1584</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6198</v>
+        <v>0.6159</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6755</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0171</v>
+        <v>0.0166</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6669</v>
+        <v>0.6589</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2353</v>
+        <v>-0.218</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1881</v>
+        <v>-0.175</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0471</v>
+        <v>-0.043</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0065</v>
+        <v>-0.0042</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0961</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0756</v>
+        <v>0.092</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.615</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2232</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.657</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5566</v>
+        <v>-1.537</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4089</v>
+        <v>-2.3989</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8619</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9094</v>
+        <v>-0.9543</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8357</v>
+        <v>-1.8693</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9263</v>
+        <v>0.9151</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6472</v>
+        <v>-0.5827</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5732</v>
+        <v>-0.5295</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0532</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0104</v>
+        <v>0.0139</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1161</v>
+        <v>0.0597</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1056</v>
+        <v>-0.0457</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9312</v>
+        <v>0.9298</v>
       </c>
       <c r="W19" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6882</v>
+        <v>-1.7807</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7466</v>
+        <v>1.396</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4347</v>
+        <v>-3.1767</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.382</v>
+        <v>-1.3641</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0554</v>
+        <v>-1.0522</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3266</v>
+        <v>-0.3119</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7729</v>
+        <v>2.6424</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2405</v>
+        <v>1.1465</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5324</v>
+        <v>1.4958</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1549</v>
+        <v>-4.0065</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2959</v>
+        <v>-2.1988</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.859</v>
+        <v>-1.8077</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0014</v>
+        <v>-1.0474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.266</v>
+        <v>-0.3737</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.6738</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3838</v>
+        <v>1.3327</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5346</v>
+        <v>1.467</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2405</v>
+        <v>-2.2009</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0238</v>
+        <v>0.9256</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2643</v>
+        <v>-3.1265</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7883</v>
+        <v>-1.7649</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7408</v>
+        <v>-0.7337</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0475</v>
+        <v>-1.0312</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0551</v>
+        <v>1.0037</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6408</v>
+        <v>0.6035</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4142</v>
+        <v>0.4002</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8434</v>
+        <v>-2.7686</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3817</v>
+        <v>-1.3372</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4617</v>
+        <v>-1.4314</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5177</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0313</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4864</v>
+        <v>-0.4636</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3361</v>
+        <v>-2.338</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6314</v>
+        <v>-2.7375</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2953</v>
+        <v>0.3995</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4506</v>
+        <v>-0.4273</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1412</v>
+        <v>-1.1276</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6906</v>
+        <v>0.7003</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5621</v>
+        <v>-0.5856</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7473</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1853</v>
+        <v>0.183</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1115</v>
+        <v>0.1583</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3939</v>
+        <v>-0.359</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5054</v>
+        <v>0.5173</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.279</v>
+        <v>-0.2729</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2256</v>
+        <v>0.1878</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5046</v>
+        <v>-0.4608</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4622</v>
+        <v>-2.4991</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7275</v>
+        <v>-1.0023</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7347</v>
+        <v>-1.4968</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8003</v>
+        <v>0.8155</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5945</v>
+        <v>-1.5485</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3948</v>
+        <v>2.3641</v>
       </c>
       <c r="J23" t="n">
-        <v>2.1532</v>
+        <v>2.0521</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1335</v>
+        <v>-0.1709</v>
       </c>
       <c r="L23" t="n">
-        <v>2.2867</v>
+        <v>2.223</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3529</v>
+        <v>-1.2366</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.461</v>
+        <v>-1.3776</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1081</v>
+        <v>0.141</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0655</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R23" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.197</v>
+        <v>-1.2088</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5203</v>
+        <v>-0.6089</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6768</v>
+        <v>-0.5999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7855</v>
+        <v>-3.7307</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6217</v>
+        <v>1.3819</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.4072</v>
+        <v>-5.1127</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1601</v>
+        <v>-2.1214</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.6425</v>
+        <v>-4.5738</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4824</v>
+        <v>2.4524</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9389</v>
+        <v>1.8376</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.1937</v>
+        <v>-2.218</v>
       </c>
       <c r="L24" t="n">
-        <v>4.1326</v>
+        <v>4.0556</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.099</v>
+        <v>-3.959</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4488</v>
+        <v>-2.3558</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6502</v>
+        <v>-1.6032</v>
       </c>
       <c r="P24" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3105</v>
+        <v>-1.3468</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2517</v>
+        <v>-0.3499</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0588</v>
+        <v>-0.9968</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="W24" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3149</v>
+        <v>-2.2625</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5686</v>
+        <v>-1.595999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>16.3081</v>
+        <v>14.3107</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.8764</v>
+        <v>-15.9068</v>
       </c>
       <c r="G25" t="n">
-        <v>2.9559</v>
+        <v>2.9775</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.0693</v>
+        <v>-8.974399999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>12.0252</v>
+        <v>11.952</v>
       </c>
       <c r="J25" t="n">
-        <v>21.424</v>
+        <v>20.5357</v>
       </c>
       <c r="K25" t="n">
-        <v>3.439099999999999</v>
+        <v>2.9394</v>
       </c>
       <c r="L25" t="n">
-        <v>17.9849</v>
+        <v>17.5962</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.468</v>
+        <v>-17.5581</v>
       </c>
       <c r="N25" t="n">
-        <v>-12.5082</v>
+        <v>-11.9138</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.9596</v>
+        <v>-5.644400000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>2.295</v>
+        <v>2.339799999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.4749</v>
+        <v>-11.6987</v>
       </c>
       <c r="R25" t="n">
-        <v>13.77</v>
+        <v>14.0382</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.7373</v>
+        <v>-5.8494</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2778</v>
+        <v>-1.9804</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.4596</v>
+        <v>-3.8689</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0819</v>
+        <v>-1.0641</v>
       </c>
       <c r="W25" t="n">
-        <v>7.6365</v>
+        <v>7.4539</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.7186</v>
+        <v>-8.518000000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105365_W4.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105365_W4.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.546</v>
+        <v>5.5864</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1906</v>
+        <v>7.3334</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6447</v>
+        <v>-1.7471</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0617</v>
+        <v>5.1126</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4174</v>
+        <v>5.4783</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3558</v>
+        <v>-0.3657</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0348</v>
+        <v>7.089</v>
       </c>
       <c r="K2" t="n">
-        <v>6.3149</v>
+        <v>6.3878</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7199</v>
+        <v>0.7012</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9731</v>
+        <v>-1.9764</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8975</v>
+        <v>-0.9095</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0757</v>
+        <v>-1.0669</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4263</v>
+        <v>0.3999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8994</v>
+        <v>0.9576</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4731</v>
+        <v>-0.5577</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4619</v>
+        <v>1.4662</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5962</v>
+        <v>1.6076</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6312</v>
+        <v>3.618</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8368</v>
+        <v>5.9476</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2056</v>
+        <v>-2.3296</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3405</v>
+        <v>2.367</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3044</v>
+        <v>1.3183</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0361</v>
+        <v>1.0486</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2617</v>
+        <v>4.2926</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0314</v>
+        <v>2.0552</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2303</v>
+        <v>2.2374</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9212</v>
+        <v>-1.9257</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.727</v>
+        <v>-0.7369</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1942</v>
+        <v>-1.1888</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5948</v>
+        <v>0.5527</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6167</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0219</v>
+        <v>-0.1192</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9298</v>
+        <v>0.9304</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4976</v>
+        <v>3.4978</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0541</v>
+        <v>5.1881</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5566</v>
+        <v>-1.6903</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2091</v>
+        <v>3.246</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5171</v>
+        <v>3.5564</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.308</v>
+        <v>-0.3104</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4624</v>
+        <v>5.5075</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7376</v>
+        <v>4.7924</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7248</v>
+        <v>0.7151</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2533</v>
+        <v>-2.2615</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2206</v>
+        <v>-1.236</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0327</v>
+        <v>-1.0255</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9359</v>
+        <v>-0.9283</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2243</v>
+        <v>1.1801</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8673</v>
+        <v>0.9296</v>
       </c>
       <c r="U4" t="n">
-        <v>0.357</v>
+        <v>0.2505</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7418</v>
+        <v>1.7431</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8236</v>
+        <v>2.9024</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0818</v>
+        <v>-1.1593</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2953</v>
+        <v>1.3264</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6448</v>
+        <v>2.6739</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3494</v>
+        <v>-1.3475</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8531</v>
+        <v>2.8836</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5236</v>
+        <v>2.5525</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3294</v>
+        <v>0.3311</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5577</v>
+        <v>-1.5572</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1211</v>
+        <v>0.1214</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6789</v>
+        <v>-1.6786</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1128</v>
+        <v>1.0939</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1404</v>
+        <v>1.1791</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0853</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1161</v>
+        <v>0.1097</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5466</v>
+        <v>2.6275</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4306</v>
+        <v>-2.5177</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7862</v>
+        <v>-0.7994</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3836</v>
+        <v>0.3872</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1698</v>
+        <v>-1.1866</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2434</v>
+        <v>2.2459</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4112</v>
+        <v>1.4274</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8321</v>
+        <v>0.8185</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0295</v>
+        <v>-3.0453</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0276</v>
+        <v>-1.0402</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0019</v>
+        <v>-2.0052</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7965</v>
+        <v>0.8205</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3033</v>
+        <v>0.3815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4932</v>
+        <v>0.4389</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1024</v>
+        <v>-0.0975</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6105</v>
+        <v>0.6762</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7129</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7546</v>
+        <v>-1.7643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2522</v>
+        <v>0.2547</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0068</v>
+        <v>-2.019</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3512</v>
+        <v>0.3422</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.376</v>
+        <v>-0.3798</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7272</v>
+        <v>0.722</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1058</v>
+        <v>-2.1065</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6282</v>
+        <v>0.6345</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.734</v>
+        <v>-2.741</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3481</v>
+        <v>0.3651</v>
       </c>
       <c r="T7" t="n">
-        <v>0.125</v>
+        <v>0.1926</v>
       </c>
       <c r="U7" t="n">
-        <v>0.223</v>
+        <v>0.1725</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,19 +1068,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.166</v>
+        <v>-0.1679</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.166</v>
+        <v>-0.1679</v>
       </c>
       <c r="G8" t="n">
-        <v>0.157</v>
+        <v>0.1586</v>
       </c>
       <c r="H8" t="n">
-        <v>0.157</v>
+        <v>0.1586</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.157</v>
+        <v>0.1586</v>
       </c>
       <c r="N8" t="n">
-        <v>0.157</v>
+        <v>0.1586</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3231</v>
+        <v>-0.3265</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3231</v>
+        <v>-0.3265</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3889</v>
+        <v>-0.4222</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9335</v>
+        <v>2.0092</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3224</v>
+        <v>-2.4313</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1842</v>
+        <v>-0.2032</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3814</v>
+        <v>-0.3871</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1972</v>
+        <v>0.1839</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4261</v>
+        <v>2.417</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8396</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5959</v>
+        <v>1.5773</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6103</v>
+        <v>-2.6201</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2116</v>
+        <v>-1.2267</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3987</v>
+        <v>-1.3934</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9414</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3165</v>
+        <v>0.2415</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7102</v>
+        <v>-1.7172</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4818</v>
+        <v>-0.4347</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2284</v>
+        <v>-1.2825</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2255</v>
+        <v>-2.2435</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8409</v>
+        <v>-0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3846</v>
+        <v>-1.3935</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2575</v>
+        <v>-0.2704</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3165</v>
+        <v>-1.3305</v>
       </c>
       <c r="L10" t="n">
-        <v>1.059</v>
+        <v>1.0601</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.968</v>
+        <v>-1.9731</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4756</v>
+        <v>0.4805</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4436</v>
+        <v>-2.4536</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5152</v>
+        <v>0.5263</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1186</v>
+        <v>-0.0757</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6338</v>
+        <v>0.602</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3602</v>
+        <v>-3.3838</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0231</v>
+        <v>-1.9981</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3371</v>
+        <v>-1.3857</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7241</v>
+        <v>-4.7669</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2791</v>
+        <v>-0.2826</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.445</v>
+        <v>-4.4842</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3132</v>
+        <v>-3.3524</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7413</v>
+        <v>-0.7492</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5719</v>
+        <v>-2.6032</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4109</v>
+        <v>-1.4145</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4622</v>
+        <v>0.4665</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8731</v>
+        <v>-1.881</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0598</v>
+        <v>0.0814</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0917</v>
+        <v>0.1412</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0319</v>
+        <v>-0.0598</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,64 +1400,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6767</v>
+        <v>-5.6859</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0521</v>
+        <v>-5.9959</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3754</v>
+        <v>0.31</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3666</v>
+        <v>-5.4101</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2007</v>
+        <v>-3.2347</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1659</v>
+        <v>-2.1754</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5038</v>
+        <v>-3.5449</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.5013</v>
+        <v>-3.538</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0024</v>
+        <v>-0.0069</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8628</v>
+        <v>-1.8652</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3006</v>
+        <v>0.3033</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1635</v>
+        <v>-2.1684</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1057</v>
+        <v>-2.0886</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6614</v>
+        <v>1.6715</v>
       </c>
       <c r="T12" t="n">
-        <v>0.827</v>
+        <v>0.8888</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8344</v>
+        <v>0.7827</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.128299999999999</v>
+        <v>3.080500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>17.4387</v>
+        <v>18.2557</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.3107</v>
+        <v>-15.1751</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.977599999999999</v>
+        <v>-2.9768</v>
       </c>
       <c r="H13" t="n">
-        <v>8.974400000000003</v>
+        <v>9.072999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.952</v>
+        <v>-12.0498</v>
       </c>
       <c r="J13" t="n">
-        <v>17.5582</v>
+        <v>17.6101</v>
       </c>
       <c r="K13" t="n">
-        <v>11.9137</v>
+        <v>12.0574</v>
       </c>
       <c r="L13" t="n">
-        <v>5.644300000000001</v>
+        <v>5.552599999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.5356</v>
+        <v>-20.5869</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.9396</v>
+        <v>-2.9845</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.5963</v>
+        <v>-17.6024</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3396</v>
+        <v>-2.3206</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.0384</v>
+        <v>-13.9244</v>
       </c>
       <c r="R13" t="n">
-        <v>11.6988</v>
+        <v>11.6038</v>
       </c>
       <c r="S13" t="n">
-        <v>7.3813</v>
+        <v>7.3063</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4009</v>
+        <v>5.9665</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9803</v>
+        <v>1.3396</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0641</v>
+        <v>1.0716</v>
       </c>
       <c r="W13" t="n">
-        <v>8.517999999999999</v>
+        <v>8.603</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.4539</v>
+        <v>-7.5313</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9316</v>
+        <v>3.9743</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6467</v>
+        <v>5.7832</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.715</v>
+        <v>-1.809</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8154</v>
+        <v>2.8344</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6554</v>
+        <v>1.6755</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1601</v>
+        <v>1.1589</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1783</v>
+        <v>5.2085</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8362</v>
+        <v>3.8818</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3421</v>
+        <v>1.3267</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3629</v>
+        <v>-2.3741</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1808</v>
+        <v>-2.2063</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1821</v>
+        <v>-0.1678</v>
       </c>
       <c r="P14" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3162</v>
+        <v>-0.3052</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2239</v>
+        <v>-0.2914</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7305</v>
+        <v>1.7489</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8902</v>
+        <v>2.8673</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9427</v>
+        <v>2.9946</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0525</v>
+        <v>-0.1274</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7606</v>
+        <v>3.7796</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5825</v>
+        <v>-0.5896</v>
       </c>
       <c r="I15" t="n">
-        <v>4.343</v>
+        <v>4.3692</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5696</v>
+        <v>3.5753</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7081</v>
+        <v>-0.7156</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2777</v>
+        <v>4.2909</v>
       </c>
       <c r="M15" t="n">
-        <v>0.191</v>
+        <v>0.2043</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1256</v>
+        <v>0.126</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0654</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2101</v>
+        <v>-1.233</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6269</v>
+        <v>-0.5807</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.6524</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3662</v>
+        <v>2.3555</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2536</v>
+        <v>1.2928</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1126</v>
+        <v>1.0627</v>
       </c>
       <c r="G16" t="n">
-        <v>1.199</v>
+        <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>0.385</v>
+        <v>0.3891</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5503</v>
+        <v>1.5574</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5645</v>
+        <v>0.571</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9858</v>
+        <v>0.9865</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3513</v>
+        <v>-0.3474</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1795</v>
+        <v>-0.1819</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1718</v>
+        <v>-0.1655</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2367</v>
+        <v>-0.247</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2968</v>
+        <v>-0.2646</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0601</v>
+        <v>0.0177</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8056</v>
+        <v>1.8226</v>
       </c>
       <c r="E17" t="n">
-        <v>3.861</v>
+        <v>3.9645</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0554</v>
+        <v>-2.1419</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1442</v>
+        <v>1.1668</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1608</v>
+        <v>1.1737</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0166</v>
+        <v>-0.0068</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5661</v>
+        <v>3.5958</v>
       </c>
       <c r="K17" t="n">
-        <v>2.507</v>
+        <v>2.5357</v>
       </c>
       <c r="L17" t="n">
-        <v>1.059</v>
+        <v>1.0601</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4218</v>
+        <v>-2.4289</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3462</v>
+        <v>-1.362</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0757</v>
+        <v>-1.0669</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3216</v>
+        <v>0.335</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2949</v>
+        <v>0.3687</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0267</v>
+        <v>-0.0337</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.553</v>
+        <v>0.5448</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5793</v>
+        <v>0.5951</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0263</v>
+        <v>-0.0504</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4575</v>
+        <v>0.4604</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1584</v>
+        <v>-0.1604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6159</v>
+        <v>0.6209</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6755</v>
+        <v>0.6791</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0166</v>
+        <v>0.0168</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6589</v>
+        <v>0.6623</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.218</v>
+        <v>-0.2186</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.175</v>
+        <v>-0.1772</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.043</v>
+        <v>-0.0414</v>
       </c>
       <c r="P18" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0042</v>
+        <v>-0.0064</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0961</v>
+        <v>-0.0839</v>
       </c>
       <c r="U18" t="n">
-        <v>0.092</v>
+        <v>0.0775</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,67 +1977,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6075</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.1277</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.657</v>
+        <v>-0.7352</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.537</v>
+        <v>-1.5486</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3989</v>
+        <v>-2.4248</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8619</v>
+        <v>0.8762</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9543</v>
+        <v>-0.9686</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8693</v>
+        <v>-1.8885</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9151</v>
+        <v>0.9198</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5827</v>
+        <v>-0.58</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5295</v>
+        <v>-0.5364</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0532</v>
+        <v>-0.0436</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0139</v>
+        <v>0.0108</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0597</v>
+        <v>0.1133</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0457</v>
+        <v>-0.1025</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9298</v>
+        <v>0.9304</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7807</v>
+        <v>-1.7281</v>
       </c>
       <c r="E20" t="n">
-        <v>1.396</v>
+        <v>1.5549</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1767</v>
+        <v>-3.2829</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3641</v>
+        <v>-1.3717</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0522</v>
+        <v>-1.0636</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3119</v>
+        <v>-0.3081</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6424</v>
+        <v>2.656</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1465</v>
+        <v>1.1614</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4958</v>
+        <v>1.4947</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.0065</v>
+        <v>-4.0277</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1988</v>
+        <v>-2.225</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8077</v>
+        <v>-1.8028</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0474</v>
+        <v>-1.0145</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3737</v>
+        <v>-0.2761</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6738</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3327</v>
+        <v>1.3544</v>
       </c>
       <c r="W20" t="n">
-        <v>1.467</v>
+        <v>1.4957</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2009</v>
+        <v>-2.2123</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9256</v>
+        <v>0.9739</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1265</v>
+        <v>-3.1863</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7649</v>
+        <v>-1.7765</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7337</v>
+        <v>-0.7417</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0312</v>
+        <v>-1.0348</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0037</v>
+        <v>1.0088</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6035</v>
+        <v>0.611</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4002</v>
+        <v>0.3978</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7686</v>
+        <v>-2.7853</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3372</v>
+        <v>-1.3527</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4314</v>
+        <v>-1.4326</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5245</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0349</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4636</v>
+        <v>-0.4896</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.338</v>
+        <v>-2.333</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7375</v>
+        <v>-2.6879</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3995</v>
+        <v>0.3548</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4273</v>
+        <v>-0.4272</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7003</v>
+        <v>0.7129</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5856</v>
+        <v>-0.5923</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.7763</v>
       </c>
       <c r="L22" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1583</v>
+        <v>0.1652</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.359</v>
+        <v>-0.3638</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5173</v>
+        <v>0.529</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2729</v>
+        <v>-0.2814</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1878</v>
+        <v>0.2252</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4608</v>
+        <v>-0.5065</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4991</v>
+        <v>-2.4893</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0023</v>
+        <v>-0.8961</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4968</v>
+        <v>-1.5932</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8155</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5485</v>
+        <v>-1.5664</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3641</v>
+        <v>2.3754</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0521</v>
+        <v>2.0449</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1709</v>
+        <v>-0.1718</v>
       </c>
       <c r="L23" t="n">
-        <v>2.223</v>
+        <v>2.2167</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2366</v>
+        <v>-1.2359</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3776</v>
+        <v>-1.3946</v>
       </c>
       <c r="O23" t="n">
-        <v>0.141</v>
+        <v>0.1588</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1057</v>
+        <v>-2.0886</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4038</v>
+        <v>1.3924</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2088</v>
+        <v>-1.2097</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6089</v>
+        <v>-0.5316</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5999</v>
+        <v>-0.6781</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7307</v>
+        <v>-3.7703</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3819</v>
+        <v>1.4725</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.1127</v>
+        <v>-5.2427</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1214</v>
+        <v>-2.1596</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.5738</v>
+        <v>-4.6247</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4524</v>
+        <v>2.4651</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8376</v>
+        <v>1.8221</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.218</v>
+        <v>-2.2411</v>
       </c>
       <c r="L24" t="n">
-        <v>4.0556</v>
+        <v>4.0632</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.959</v>
+        <v>-3.9817</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.3558</v>
+        <v>-2.3836</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6032</v>
+        <v>-1.5981</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3468</v>
+        <v>-1.3259</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3499</v>
+        <v>-0.261</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9968</v>
+        <v>-1.0649</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2625</v>
+        <v>-2.2848</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.595999999999999</v>
+        <v>-1.576</v>
       </c>
       <c r="E25" t="n">
-        <v>14.3107</v>
+        <v>15.1752</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.9068</v>
+        <v>-16.7515</v>
       </c>
       <c r="G25" t="n">
-        <v>2.9775</v>
+        <v>2.9766</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.974399999999999</v>
+        <v>-9.073</v>
       </c>
       <c r="I25" t="n">
-        <v>11.952</v>
+        <v>12.0499</v>
       </c>
       <c r="J25" t="n">
-        <v>20.5357</v>
+        <v>20.587</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9394</v>
+        <v>2.984399999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>17.5962</v>
+        <v>17.6027</v>
       </c>
       <c r="M25" t="n">
-        <v>-17.5581</v>
+        <v>-17.6101</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.9138</v>
+        <v>-12.0575</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.644400000000001</v>
+        <v>-5.552600000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>2.339799999999999</v>
+        <v>2.3208</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.6987</v>
+        <v>-11.6037</v>
       </c>
       <c r="R25" t="n">
-        <v>14.0382</v>
+        <v>13.9242</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.8494</v>
+        <v>-5.8018</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.9804</v>
+        <v>-1.3394</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.8689</v>
+        <v>-4.4623</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0641</v>
+        <v>-1.0716</v>
       </c>
       <c r="W25" t="n">
-        <v>7.4539</v>
+        <v>7.5314</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.518000000000001</v>
+        <v>-8.603100000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
